--- a/6.1 Myrmidon disturbance/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/6.1 Myrmidon disturbance/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -776,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>58.53277987489908</v>
+        <v>56.09019158673302</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7343472827766142</v>
+        <v>0.9424777960769379</v>
       </c>
       <c r="D2" t="n">
-        <v>82.4422634641259</v>
+        <v>97.83999445753287</v>
       </c>
     </row>
     <row r="3">
@@ -790,13 +790,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>161.1882468217626</v>
+        <v>152.8826612438345</v>
       </c>
       <c r="C3" t="n">
-        <v>5.25725895624167</v>
+        <v>5.861033794353458</v>
       </c>
       <c r="D3" t="n">
-        <v>106.9270512080413</v>
+        <v>117.0734137314321</v>
       </c>
     </row>
     <row r="4">
@@ -804,13 +804,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>220.3483634796754</v>
+        <v>207.1389481190345</v>
       </c>
       <c r="C4" t="n">
-        <v>13.13283903970958</v>
+        <v>13.41361888312417</v>
       </c>
       <c r="D4" t="n">
-        <v>73.19420009012096</v>
+        <v>80.63486594060753</v>
       </c>
     </row>
     <row r="5">
@@ -818,13 +818,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>235.5703616340222</v>
+        <v>223.6912144126358</v>
       </c>
       <c r="C5" t="n">
-        <v>13.49903093339365</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D5" t="n">
-        <v>39.07355862902306</v>
+        <v>48.15472489330606</v>
       </c>
     </row>
     <row r="6">
@@ -832,13 +832,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254.9942399625453</v>
+        <v>242.4759749856943</v>
       </c>
       <c r="C6" t="n">
-        <v>8.533351045313278</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="D6" t="n">
-        <v>36.18623863083319</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -846,13 +846,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299.3731631853181</v>
+        <v>289.6116457619921</v>
       </c>
       <c r="C7" t="n">
-        <v>4.790928796724434</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -860,13 +860,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296.9099581953628</v>
+        <v>312.7651836189488</v>
       </c>
       <c r="C8" t="n">
-        <v>3.838633523605028</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31671326450677</v>
+        <v>46.39739650270425</v>
       </c>
     </row>
     <row r="9">
@@ -874,13 +874,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134.8999885451457</v>
+        <v>178.4984223430423</v>
       </c>
       <c r="C9" t="n">
-        <v>3.993749660876023</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="D9" t="n">
-        <v>55.80155776168444</v>
+        <v>53.58280795008665</v>
       </c>
     </row>
     <row r="10">
@@ -888,13 +888,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25.62361508084176</v>
+        <v>37.01188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>60.50020227420969</v>
+        <v>59.64608177151497</v>
       </c>
     </row>
     <row r="11">
@@ -902,13 +902,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.37256540599505</v>
+        <v>10.30638739918301</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>62.72680606744144</v>
+        <v>65.03685841553418</v>
       </c>
     </row>
     <row r="12">
@@ -916,13 +916,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="C12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>62.70324412253953</v>
+        <v>65.74077151947915</v>
       </c>
     </row>
     <row r="13">
@@ -930,13 +930,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>67.64241682260524</v>
       </c>
     </row>
     <row r="14">
@@ -944,13 +944,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.682175785731292</v>
+        <v>9.21861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>55.9262397201238</v>
+        <v>65.14485066300135</v>
       </c>
     </row>
     <row r="15">
@@ -958,13 +958,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>46.58392856651115</v>
+        <v>65.21749999311561</v>
       </c>
     </row>
     <row r="16">
@@ -972,13 +972,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>33.47857846252048</v>
+        <v>64.89057800760142</v>
       </c>
     </row>
     <row r="17">
@@ -986,13 +986,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -1000,13 +1000,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>3.21031499288707</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="D18" t="n">
-        <v>5.885577486959628</v>
+        <v>47.08461989567702</v>
       </c>
     </row>
     <row r="19">
@@ -1014,13 +1014,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>1.203622685406589</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6018113427032947</v>
+        <v>38.51592593301086</v>
       </c>
     </row>
     <row r="20">
@@ -1028,13 +1028,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>25.55489274154447</v>
       </c>
     </row>
     <row r="21">
@@ -1042,13 +1042,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>23.20591513420485</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15.7800222912593</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.712946421472776</v>
       </c>
     </row>
   </sheetData>
@@ -1087,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>71.80208184549898</v>
+        <v>67.68070498307085</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6322455215349458</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D2" t="n">
-        <v>69.4665040570958</v>
+        <v>82.92135634379835</v>
       </c>
     </row>
     <row r="3">
@@ -1101,13 +1101,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>198.7204615551181</v>
+        <v>184.833640278547</v>
       </c>
       <c r="C3" t="n">
-        <v>4.663301595172349</v>
+        <v>5.291620125890308</v>
       </c>
       <c r="D3" t="n">
-        <v>112.7586325712674</v>
+        <v>123.5480398409399</v>
       </c>
     </row>
     <row r="4">
@@ -1115,13 +1115,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>298.5327871504829</v>
+        <v>274.0666526129481</v>
       </c>
       <c r="C4" t="n">
-        <v>12.94139823738145</v>
+        <v>13.3115171218825</v>
       </c>
       <c r="D4" t="n">
-        <v>76.8571007746658</v>
+        <v>85.99520840579511</v>
       </c>
     </row>
     <row r="5">
@@ -1129,13 +1129,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>305.9125846433062</v>
+        <v>283.0624068269616</v>
       </c>
       <c r="C5" t="n">
-        <v>15.0207398749762</v>
+        <v>15.73250696055514</v>
       </c>
       <c r="D5" t="n">
-        <v>40.0307626406637</v>
+        <v>50.31456984264904</v>
       </c>
     </row>
     <row r="6">
@@ -1143,13 +1143,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310.5415250688299</v>
+        <v>291.703750119742</v>
       </c>
       <c r="C6" t="n">
-        <v>10.30442390377452</v>
+        <v>11.35096695650162</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26674194258143</v>
+        <v>36.87051678069322</v>
       </c>
     </row>
     <row r="7">
@@ -1157,13 +1157,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>327.400096646156</v>
+        <v>307.7572885795859</v>
       </c>
       <c r="C7" t="n">
-        <v>5.689227946110266</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -1171,13 +1171,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338.0500957418254</v>
+        <v>337.5494044126596</v>
       </c>
       <c r="C8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="D8" t="n">
-        <v>47.89947049020188</v>
+        <v>45.72980806381643</v>
       </c>
     </row>
     <row r="9">
@@ -1185,13 +1185,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>225.6468558394953</v>
+        <v>274.0156017323272</v>
       </c>
       <c r="C9" t="n">
-        <v>3.993749660876023</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="D9" t="n">
-        <v>55.46874528994476</v>
+        <v>53.24999547834697</v>
       </c>
     </row>
     <row r="10">
@@ -1199,13 +1199,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>74.02377690020951</v>
+        <v>120.0039306286089</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>59.36137493728339</v>
+        <v>58.64960785170445</v>
       </c>
     </row>
     <row r="11">
@@ -1213,13 +1213,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16.70345544005523</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>61.66062806062941</v>
+        <v>63.97068040872215</v>
       </c>
     </row>
     <row r="12">
@@ -1227,13 +1227,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="C12" t="n">
-        <v>3.688426124855267</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>61.18448042406971</v>
+        <v>64.65594030628644</v>
       </c>
     </row>
     <row r="13">
@@ -1241,13 +1241,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>58.27654372409067</v>
+        <v>66.60176425610362</v>
       </c>
     </row>
     <row r="14">
@@ -1255,13 +1255,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.989462817160544</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="D14" t="n">
-        <v>52.54608237440203</v>
+        <v>64.2229895687136</v>
       </c>
     </row>
     <row r="15">
@@ -1269,13 +1269,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>42.64221153396021</v>
+        <v>64.14248625696536</v>
       </c>
     </row>
     <row r="16">
@@ -1283,13 +1283,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>28.51878906066559</v>
+        <v>64.47726222411352</v>
       </c>
     </row>
     <row r="17">
@@ -1297,13 +1297,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
         <v>4.249985811684442</v>
       </c>
       <c r="D17" t="n">
-        <v>14.16661937228147</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -1311,13 +1311,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.140209995258047</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>2.140209995258047</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="D18" t="n">
-        <v>3.745367491701582</v>
+        <v>46.014514898048</v>
       </c>
     </row>
     <row r="19">
@@ -1325,13 +1325,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>37.91411459030757</v>
       </c>
     </row>
     <row r="20">
@@ -1339,13 +1339,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24.8823955641354</v>
       </c>
     </row>
     <row r="21">
@@ -1353,13 +1353,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22.66958655411793</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>16.05762380916687</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.778264425686323</v>
       </c>
     </row>
   </sheetData>
@@ -1398,13 +1398,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>82.17817333168351</v>
+        <v>76.17871311103124</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4643666641087413</v>
+        <v>0.6194828013797373</v>
       </c>
       <c r="D2" t="n">
-        <v>78.67038878440965</v>
+        <v>96.22600123175113</v>
       </c>
     </row>
     <row r="3">
@@ -1412,13 +1412,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>238.7168630261332</v>
+        <v>216.3624678004333</v>
       </c>
       <c r="C3" t="n">
-        <v>4.187153958612646</v>
+        <v>4.795837535245669</v>
       </c>
       <c r="D3" t="n">
-        <v>116.1113009812703</v>
+        <v>127.1265102229195</v>
       </c>
     </row>
     <row r="4">
@@ -1426,13 +1426,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>362.3336252063703</v>
+        <v>329.6610616090365</v>
       </c>
       <c r="C4" t="n">
-        <v>12.54575391256999</v>
+        <v>12.96692367769187</v>
       </c>
       <c r="D4" t="n">
-        <v>80.7497304220044</v>
+        <v>91.58527983377644</v>
       </c>
     </row>
     <row r="5">
@@ -1440,13 +1440,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>396.4297229748622</v>
+        <v>357.8961255831748</v>
       </c>
       <c r="C5" t="n">
-        <v>16.02703127182918</v>
+        <v>16.51790512395259</v>
       </c>
       <c r="D5" t="n">
-        <v>41.47884050442774</v>
+        <v>52.71985171805373</v>
       </c>
     </row>
     <row r="6">
@@ -1454,13 +1454,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>383.1957639216151</v>
+        <v>353.0070220160257</v>
       </c>
       <c r="C6" t="n">
-        <v>11.91449013873929</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -1468,13 +1468,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>372.3749407254066</v>
+        <v>342.0124294761656</v>
       </c>
       <c r="C7" t="n">
-        <v>6.587527095496098</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="D7" t="n">
-        <v>41.56130731158447</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -1482,13 +1482,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367.42398705289</v>
+        <v>356.9094691404067</v>
       </c>
       <c r="C8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="D8" t="n">
-        <v>47.398779161036</v>
+        <v>45.06221962492859</v>
       </c>
     </row>
     <row r="9">
@@ -1496,13 +1496,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>291.21091277221</v>
+        <v>326.7109097577747</v>
       </c>
       <c r="C9" t="n">
-        <v>4.104687151455913</v>
+        <v>3.882812170296134</v>
       </c>
       <c r="D9" t="n">
-        <v>54.58124536530566</v>
+        <v>52.36249555370786</v>
       </c>
     </row>
     <row r="10">
@@ -1510,13 +1510,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>131.5345574149877</v>
+        <v>204.988920646734</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>58.2225476003571</v>
+        <v>57.65313393189394</v>
       </c>
     </row>
     <row r="11">
@@ -1524,13 +1524,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33.58460721457913</v>
+        <v>70.72314111853171</v>
       </c>
       <c r="C11" t="n">
         <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>60.59445005381736</v>
+        <v>62.90450240191011</v>
       </c>
     </row>
     <row r="12">
@@ -1538,13 +1538,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.58404207303562</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="C12" t="n">
-        <v>3.688426124855267</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>59.44875048296136</v>
+        <v>63.5711090930937</v>
       </c>
     </row>
     <row r="13">
@@ -1552,13 +1552,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>55.93507544946203</v>
+        <v>65.561111689602</v>
       </c>
     </row>
     <row r="14">
@@ -1566,13 +1566,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.989462817160544</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="D14" t="n">
-        <v>49.16592502868027</v>
+        <v>63.91570253728435</v>
       </c>
     </row>
     <row r="15">
@@ -1580,13 +1580,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.091744504851459</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>38.70049450140926</v>
+        <v>63.06747252081509</v>
       </c>
     </row>
     <row r="16">
@@ -1594,13 +1594,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>23.97231544229862</v>
+        <v>63.23731487364979</v>
       </c>
     </row>
     <row r="17">
@@ -1608,13 +1608,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
+        <v>6.138868394655306</v>
+      </c>
+      <c r="C17" t="n">
         <v>3.777765165941727</v>
       </c>
-      <c r="C17" t="n">
-        <v>3.305544520199011</v>
-      </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -1622,13 +1622,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="19">
@@ -1636,13 +1636,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>37.31230324760427</v>
       </c>
     </row>
     <row r="20">
@@ -1650,13 +1650,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24.8823955641354</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22.05604850233784</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>16.30229671911928</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.835834522145711</v>
       </c>
     </row>
   </sheetData>
@@ -1709,13 +1709,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>87.76628126425636</v>
+        <v>79.66391746110742</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3661918936840602</v>
+        <v>0.5016730768701201</v>
       </c>
       <c r="D2" t="n">
-        <v>69.77575458393355</v>
+        <v>85.26478811383548</v>
       </c>
     </row>
     <row r="3">
@@ -1723,13 +1723,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>266.8292085372406</v>
+        <v>238.5057872697201</v>
       </c>
       <c r="C3" t="n">
-        <v>3.73064127613788</v>
+        <v>4.304963683122264</v>
       </c>
       <c r="D3" t="n">
-        <v>118.6736624893544</v>
+        <v>133.7729421806704</v>
       </c>
     </row>
     <row r="4">
@@ -1737,13 +1737,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>423.6074446715265</v>
+        <v>372.964971095659</v>
       </c>
       <c r="C4" t="n">
-        <v>12.06077054667207</v>
+        <v>12.49470303194916</v>
       </c>
       <c r="D4" t="n">
-        <v>82.5365112437336</v>
+        <v>94.80148531288899</v>
       </c>
     </row>
     <row r="5">
@@ -1751,13 +1751,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>483.2653074154925</v>
+        <v>426.1521347209343</v>
       </c>
       <c r="C5" t="n">
-        <v>16.46881773874025</v>
+        <v>16.88606051304514</v>
       </c>
       <c r="D5" t="n">
-        <v>41.72427743048944</v>
+        <v>54.14338588921161</v>
       </c>
     </row>
     <row r="6">
@@ -1765,13 +1765,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>465.7921617753078</v>
+        <v>425.6210092129367</v>
       </c>
       <c r="C6" t="n">
-        <v>13.36354975020759</v>
+        <v>14.77235770580176</v>
       </c>
       <c r="D6" t="n">
-        <v>35.38120551335081</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -1779,13 +1779,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>427.2310754479014</v>
+        <v>388.5443254143516</v>
       </c>
       <c r="C7" t="n">
-        <v>7.60559946480004</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -1793,13 +1793,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>403.9744540819988</v>
+        <v>377.2709165264855</v>
       </c>
       <c r="C8" t="n">
-        <v>4.589670517353839</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="D8" t="n">
-        <v>46.89808783187013</v>
+        <v>44.39463118604076</v>
       </c>
     </row>
     <row r="9">
@@ -1807,13 +1807,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>332.5905967585088</v>
+        <v>361.1015318375404</v>
       </c>
       <c r="C9" t="n">
         <v>4.104687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>53.69374544066654</v>
+        <v>51.47499562906875</v>
       </c>
     </row>
     <row r="10">
@@ -1821,13 +1821,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>183.4935546622501</v>
+        <v>264.4926490011332</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>57.51078051477815</v>
+        <v>56.65666001208344</v>
       </c>
     </row>
     <row r="11">
@@ -1835,13 +1835,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56.68513069550657</v>
+        <v>128.119057151913</v>
       </c>
       <c r="C11" t="n">
-        <v>3.731623023842126</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>58.81748670913064</v>
+        <v>62.3714133985041</v>
       </c>
     </row>
     <row r="12">
@@ -1849,13 +1849,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16.05550195525234</v>
+        <v>37.5351599764683</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="D12" t="n">
-        <v>57.71302054185299</v>
+        <v>62.48627787990098</v>
       </c>
     </row>
     <row r="13">
@@ -1863,13 +1863,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.14636252339079</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>53.59360717483338</v>
+        <v>64.26029598147498</v>
       </c>
     </row>
     <row r="14">
@@ -1877,13 +1877,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.989462817160544</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="D14" t="n">
-        <v>46.09305471438775</v>
+        <v>62.68655441156734</v>
       </c>
     </row>
     <row r="15">
@@ -1891,13 +1891,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>34.04210164475815</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -1905,13 +1905,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>4.133157834879071</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>61.99736752318607</v>
       </c>
     </row>
     <row r="17">
@@ -1919,13 +1919,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.833323874456295</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>2.361103228713579</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="D17" t="n">
-        <v>7.555530331883453</v>
+        <v>52.88871232318417</v>
       </c>
     </row>
     <row r="18">
@@ -1933,13 +1933,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>43.87430490278995</v>
       </c>
     </row>
     <row r="19">
@@ -1947,13 +1947,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="20">
@@ -1961,13 +1961,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24.20989838672634</v>
       </c>
     </row>
     <row r="21">
@@ -1975,13 +1975,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>21.36805866777667</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15.54040630383758</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.885101575959396</v>
       </c>
     </row>
   </sheetData>
@@ -2020,13 +2020,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>94.07990075026758</v>
+        <v>84.08374562562656</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2856885819358218</v>
+        <v>0.3995713156284518</v>
       </c>
       <c r="D2" t="n">
-        <v>74.88084264601696</v>
+        <v>93.65284049892023</v>
       </c>
     </row>
     <row r="3">
@@ -2034,13 +2034,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>282.8120611623787</v>
+        <v>249.3835518327748</v>
       </c>
       <c r="C3" t="n">
-        <v>3.337942194439155</v>
+        <v>3.872994693253667</v>
       </c>
       <c r="D3" t="n">
-        <v>120.0186568441726</v>
+        <v>134.7988685316083</v>
       </c>
     </row>
     <row r="4">
@@ -2048,13 +2048,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>468.4045924163084</v>
+        <v>405.1653140472501</v>
       </c>
       <c r="C4" t="n">
-        <v>11.40987181875643</v>
+        <v>11.84380430403352</v>
       </c>
       <c r="D4" t="n">
-        <v>84.36158022592842</v>
+        <v>98.28570791526093</v>
       </c>
     </row>
     <row r="5">
@@ -2062,13 +2062,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>556.4545987670922</v>
+        <v>486.3823563764761</v>
       </c>
       <c r="C5" t="n">
-        <v>16.81242943522663</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="D5" t="n">
-        <v>41.99425804915732</v>
+        <v>55.66509483079416</v>
       </c>
     </row>
     <row r="6">
@@ -2076,13 +2076,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>556.2778841803278</v>
+        <v>490.6274334496393</v>
       </c>
       <c r="C6" t="n">
-        <v>14.49059611468292</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -2090,13 +2090,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>485.1414272783081</v>
+        <v>443.999326236437</v>
       </c>
       <c r="C7" t="n">
-        <v>8.444012004226815</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="D7" t="n">
-        <v>40.72289477215769</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -2104,13 +2104,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>439.4400898979148</v>
+        <v>405.1427338500524</v>
       </c>
       <c r="C8" t="n">
-        <v>4.840016181936775</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="D8" t="n">
-        <v>46.39739650270425</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="9">
@@ -2118,13 +2118,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>369.8655935933517</v>
+        <v>381.0702801419205</v>
       </c>
       <c r="C9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>53.24999547834697</v>
+        <v>51.14218315732908</v>
       </c>
     </row>
     <row r="10">
@@ -2132,13 +2132,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>221.2172101979338</v>
+        <v>309.9033890610694</v>
       </c>
       <c r="C10" t="n">
         <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>56.22959976073607</v>
+        <v>55.66018609227292</v>
       </c>
     </row>
     <row r="11">
@@ -2146,13 +2146,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.31874317984003</v>
+        <v>177.3409417997353</v>
       </c>
       <c r="C11" t="n">
-        <v>3.553926689373453</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>57.57361236784993</v>
+        <v>61.12753905722339</v>
       </c>
     </row>
     <row r="12">
@@ -2160,13 +2160,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21.04572553593887</v>
+        <v>67.91043394586461</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>55.326391872829</v>
+        <v>61.40144666670826</v>
       </c>
     </row>
     <row r="13">
@@ -2174,13 +2174,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.40652566501619</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>51.51230204183015</v>
+        <v>62.95948027334796</v>
       </c>
     </row>
     <row r="14">
@@ -2188,13 +2188,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.37488875430204</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>3.994731408580272</v>
+        <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>42.40561033723673</v>
+        <v>61.45740628585034</v>
       </c>
     </row>
     <row r="15">
@@ -2202,13 +2202,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>60.91744504851458</v>
       </c>
     </row>
     <row r="16">
@@ -2216,13 +2216,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.133157834879071</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>16.11931555602838</v>
+        <v>60.75742017272236</v>
       </c>
     </row>
     <row r="17">
@@ -2230,13 +2230,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.888882582970863</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>1.888882582970863</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="D17" t="n">
-        <v>5.194427103169874</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -2244,13 +2244,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>42.80419990516094</v>
       </c>
     </row>
     <row r="19">
@@ -2258,13 +2258,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>35.50686921949439</v>
       </c>
     </row>
     <row r="20">
@@ -2272,13 +2272,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>23.53740120931727</v>
       </c>
     </row>
     <row r="21">
@@ -2286,13 +2286,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>20.61792488333535</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>14.72708920238239</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.927223787301971</v>
       </c>
     </row>
   </sheetData>
@@ -2331,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>93.70094613642833</v>
+        <v>82.09767001993526</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2581996462169112</v>
+        <v>0.3661918936840602</v>
       </c>
       <c r="D2" t="n">
-        <v>60.50314751732243</v>
+        <v>75.88713404286995</v>
       </c>
     </row>
     <row r="3">
@@ -2345,13 +2345,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>294.7992006312322</v>
+        <v>255.8238167726338</v>
       </c>
       <c r="C3" t="n">
-        <v>2.974695543867835</v>
+        <v>3.480295611554943</v>
       </c>
       <c r="D3" t="n">
-        <v>121.8987036978052</v>
+        <v>136.7623639401019</v>
       </c>
     </row>
     <row r="4">
@@ -2359,13 +2359,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>495.180779301936</v>
+        <v>421.1825278420368</v>
       </c>
       <c r="C4" t="n">
-        <v>10.87383757223767</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="D4" t="n">
-        <v>86.37809001045136</v>
+        <v>101.6167778757704</v>
       </c>
     </row>
     <row r="5">
@@ -2373,13 +2373,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>615.7030727183873</v>
+        <v>526.8058180988386</v>
       </c>
       <c r="C5" t="n">
-        <v>16.73879835740812</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="D5" t="n">
-        <v>41.87153958612647</v>
+        <v>57.26043485019522</v>
       </c>
     </row>
     <row r="6">
@@ -2387,13 +2387,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>631.4679773531825</v>
+        <v>551.4879371313076</v>
       </c>
       <c r="C6" t="n">
-        <v>15.45663585566179</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>40.13090090649688</v>
       </c>
     </row>
     <row r="7">
@@ -2401,13 +2401,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>554.7895546606895</v>
+        <v>498.8554609589317</v>
       </c>
       <c r="C7" t="n">
-        <v>9.162651323735481</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -2415,13 +2415,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>470.6498494159209</v>
+        <v>439.1897442333319</v>
       </c>
       <c r="C8" t="n">
-        <v>5.17381040138069</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="D8" t="n">
-        <v>45.8132566186774</v>
+        <v>42.97600575340412</v>
       </c>
     </row>
     <row r="9">
@@ -2429,13 +2429,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>400.3734035028213</v>
+        <v>399.2640285970224</v>
       </c>
       <c r="C9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>52.25155806312797</v>
+        <v>50.25468323268996</v>
       </c>
     </row>
     <row r="10">
@@ -2443,13 +2443,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>249.9726004553229</v>
+        <v>337.0928917301849</v>
       </c>
       <c r="C10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>54.94841900669398</v>
+        <v>54.6637121724624</v>
       </c>
     </row>
     <row r="11">
@@ -2457,13 +2457,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>99.50994730245667</v>
+        <v>221.2319364134974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.37623035490478</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>56.15204169210055</v>
+        <v>60.06136105041135</v>
       </c>
     </row>
     <row r="12">
@@ -2471,13 +2471,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>25.38505038870978</v>
+        <v>98.93660664317655</v>
       </c>
       <c r="C12" t="n">
         <v>3.471459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>53.59066193172063</v>
+        <v>60.31661545351553</v>
       </c>
     </row>
     <row r="13">
@@ -2485,13 +2485,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.14636252339079</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="C13" t="n">
-        <v>3.642283982755667</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>48.6505074839507</v>
+        <v>61.65866456522093</v>
       </c>
     </row>
     <row r="14">
@@ -2499,13 +2499,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.760314691443536</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>3.68744437715102</v>
+        <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>38.71816596008571</v>
+        <v>60.22825816013332</v>
       </c>
     </row>
     <row r="15">
@@ -2513,13 +2513,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>3.583379120500858</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>25.80032966760617</v>
+        <v>60.20076922441442</v>
       </c>
     </row>
     <row r="16">
@@ -2527,13 +2527,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3.306526267903257</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
         <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>12.39947350463721</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -2541,13 +2541,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>1.416661937228147</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="D17" t="n">
-        <v>3.305544520199011</v>
+        <v>51.47205038595602</v>
       </c>
     </row>
     <row r="18">
@@ -2555,13 +2555,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>41.7340949075319</v>
       </c>
     </row>
     <row r="19">
@@ -2569,13 +2569,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -2583,13 +2583,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>22.86490403190821</v>
       </c>
     </row>
     <row r="21">
@@ -2597,13 +2597,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>19.81442488052193</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13.87009741636535</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.962884976104385</v>
       </c>
     </row>
   </sheetData>
@@ -2642,13 +2642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>75.57395652521522</v>
+        <v>69.44392385989813</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2748893571891069</v>
+        <v>0.3730641276137879</v>
       </c>
       <c r="D2" t="n">
-        <v>50.7435935894049</v>
+        <v>63.07336300704058</v>
       </c>
     </row>
     <row r="3">
@@ -2656,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>352.0792704355124</v>
+        <v>288.8547182820178</v>
       </c>
       <c r="C3" t="n">
-        <v>4.236241343824987</v>
+        <v>4.732023934469626</v>
       </c>
       <c r="D3" t="n">
-        <v>113.9269123393211</v>
+        <v>128.8543861823939</v>
       </c>
     </row>
     <row r="4">
@@ -2670,13 +2670,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>451.9279206959342</v>
+        <v>382.2945195291165</v>
       </c>
       <c r="C4" t="n">
-        <v>13.37533072265855</v>
+        <v>13.56677152498667</v>
       </c>
       <c r="D4" t="n">
-        <v>71.39465654823654</v>
+        <v>87.1693786600743</v>
       </c>
     </row>
     <row r="5">
@@ -2684,13 +2684,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>355.760824326438</v>
+        <v>310.6986047015093</v>
       </c>
       <c r="C5" t="n">
-        <v>10.99557428756428</v>
+        <v>12.02640937702343</v>
       </c>
       <c r="D5" t="n">
-        <v>37.40458753180348</v>
+        <v>47.93383165985053</v>
       </c>
     </row>
     <row r="6">
@@ -2698,13 +2698,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>344.5139226265865</v>
+        <v>309.7767436072216</v>
       </c>
       <c r="C6" t="n">
-        <v>5.997496725243765</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -2712,13 +2712,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312.0691244966378</v>
+        <v>291.2285842308866</v>
       </c>
       <c r="C7" t="n">
-        <v>3.593196597543325</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -2726,13 +2726,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>278.2174819065036</v>
+        <v>277.4664449127548</v>
       </c>
       <c r="C8" t="n">
-        <v>3.087596529856218</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -2740,13 +2740,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>179.9406097205808</v>
+        <v>242.7312293887983</v>
       </c>
       <c r="C9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -2754,13 +2754,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>73.59671664886216</v>
+        <v>163.7064296831556</v>
       </c>
       <c r="C10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="D10" t="n">
-        <v>43.98720588877834</v>
+        <v>47.11898106532567</v>
       </c>
     </row>
     <row r="11">
@@ -2768,13 +2768,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>19.19120412261664</v>
+        <v>74.81015681131117</v>
       </c>
       <c r="C11" t="n">
         <v>2.665445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>43.00251294141878</v>
+        <v>48.33340297547896</v>
       </c>
     </row>
     <row r="12">
@@ -2782,13 +2782,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="C12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>39.70482240285375</v>
+        <v>50.33616829214246</v>
       </c>
     </row>
     <row r="13">
@@ -2796,13 +2796,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="C13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>49.95132319207772</v>
       </c>
     </row>
     <row r="14">
@@ -2810,13 +2810,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3.68744437715102</v>
+        <v>6.760314691443536</v>
       </c>
       <c r="C14" t="n">
-        <v>2.765583282863265</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>21.51009220004762</v>
+        <v>50.39507315439727</v>
       </c>
     </row>
     <row r="15">
@@ -2824,13 +2824,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.5083653843506</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
         <v>2.150027472300515</v>
       </c>
       <c r="D15" t="n">
-        <v>10.39179944945249</v>
+        <v>50.52564559906209</v>
       </c>
     </row>
     <row r="16">
@@ -2838,13 +2838,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>2.479894700927443</v>
+        <v>43.81147304971816</v>
       </c>
     </row>
     <row r="17">
@@ -2852,13 +2852,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.888882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -2880,13 +2880,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>19.85977430920873</v>
       </c>
     </row>
     <row r="20">
@@ -2894,13 +2894,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2.017491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -2953,13 +2953,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.616218763097507</v>
+        <v>9.734028487607125</v>
       </c>
       <c r="C2" t="n">
-        <v>3.29965403397353</v>
+        <v>3.507784547273853</v>
       </c>
       <c r="D2" t="n">
-        <v>16.06630117999905</v>
+        <v>16.82617390308608</v>
       </c>
     </row>
     <row r="3">
@@ -2967,13 +2967,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6135923151542565</v>
+        <v>0.5890486225480862</v>
       </c>
       <c r="C3" t="n">
-        <v>0.849211764173491</v>
+        <v>0.8393942871310229</v>
       </c>
       <c r="D3" t="n">
-        <v>38.6612245932394</v>
+        <v>38.12617209442488</v>
       </c>
     </row>
     <row r="4">
@@ -2981,13 +2981,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.981968688425063</v>
+        <v>3.905392367493812</v>
       </c>
       <c r="C4" t="n">
-        <v>2.756747553525043</v>
+        <v>2.705696672904209</v>
       </c>
       <c r="D4" t="n">
-        <v>80.13711985455438</v>
+        <v>80.58381505998669</v>
       </c>
     </row>
     <row r="5">
@@ -2995,13 +2995,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8.909360416039807</v>
+        <v>8.762098260402784</v>
       </c>
       <c r="C5" t="n">
-        <v>3.190680038802134</v>
+        <v>3.264311116620645</v>
       </c>
       <c r="D5" t="n">
-        <v>39.09810232162923</v>
+        <v>40.6934423410303</v>
       </c>
     </row>
     <row r="6">
@@ -3009,13 +3009,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.68556299720054</v>
+        <v>13.36354975020759</v>
       </c>
       <c r="C6" t="n">
-        <v>4.467933802027235</v>
+        <v>4.387430490278996</v>
       </c>
       <c r="D6" t="n">
-        <v>56.35231822376692</v>
+        <v>55.42653013866219</v>
       </c>
     </row>
     <row r="7">
@@ -3023,13 +3023,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>6.108434215823654</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="D7" t="n">
-        <v>77.73281972685395</v>
+        <v>76.71474735755001</v>
       </c>
     </row>
     <row r="8">
@@ -3037,13 +3037,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.94835258676919</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="C8" t="n">
-        <v>7.677267047210056</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="D8" t="n">
-        <v>97.38446352276235</v>
+        <v>96.38308086443061</v>
       </c>
     </row>
     <row r="9">
@@ -3051,13 +3051,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27.06874770149305</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="C9" t="n">
-        <v>9.207811718130833</v>
+        <v>9.096874227550941</v>
       </c>
       <c r="D9" t="n">
-        <v>119.1468648828014</v>
+        <v>117.3718650335231</v>
       </c>
     </row>
     <row r="10">
@@ -3065,13 +3065,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>10.53415286656828</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="D10" t="n">
-        <v>132.9580915861455</v>
+        <v>133.8122120888403</v>
       </c>
     </row>
     <row r="11">
@@ -3079,13 +3079,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="C11" t="n">
         <v>11.19486907152638</v>
       </c>
       <c r="D11" t="n">
-        <v>148.731831950279</v>
+        <v>148.0210466124043</v>
       </c>
     </row>
     <row r="12">
@@ -3093,13 +3093,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30.8092064546734</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="C12" t="n">
         <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>153.3951335454514</v>
+        <v>153.1781673028128</v>
       </c>
     </row>
     <row r="13">
@@ -3107,13 +3107,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="C13" t="n">
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>157.6588638249953</v>
+        <v>158.4393532498715</v>
       </c>
     </row>
     <row r="14">
@@ -3121,13 +3121,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>32.87971236292993</v>
+        <v>32.26513830007143</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>157.0236730603476</v>
+        <v>157.9455341546354</v>
       </c>
     </row>
     <row r="15">
@@ -3135,13 +3135,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>38.70049450140926</v>
+        <v>35.83379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>160.1770466863883</v>
+        <v>160.8937225104885</v>
       </c>
     </row>
     <row r="16">
@@ -3149,13 +3149,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>39.67831521483909</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>151.273576756574</v>
+        <v>160.7798397767959</v>
       </c>
     </row>
     <row r="17">
@@ -3163,13 +3163,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>42.02763747110171</v>
+        <v>41.55541682535899</v>
       </c>
       <c r="C17" t="n">
-        <v>21.24992905842221</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>130.8051188707323</v>
+        <v>136.4717666196449</v>
       </c>
     </row>
     <row r="18">
@@ -3177,13 +3177,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>45.47946239923349</v>
+        <v>44.40935740160447</v>
       </c>
       <c r="C18" t="n">
-        <v>23.54230994783851</v>
+        <v>23.007257449024</v>
       </c>
       <c r="D18" t="n">
-        <v>111.8259722522329</v>
+        <v>119.8517597344506</v>
       </c>
     </row>
     <row r="19">
@@ -3191,13 +3191,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>46.94128473085699</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="C19" t="n">
-        <v>27.08151042164826</v>
+        <v>25.87788773624167</v>
       </c>
       <c r="D19" t="n">
-        <v>83.04996529305467</v>
+        <v>96.89162617523046</v>
       </c>
     </row>
     <row r="20">
@@ -3205,13 +3205,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>48.41979677345267</v>
+        <v>49.09229395086174</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>28.91737862858979</v>
       </c>
       <c r="D20" t="n">
-        <v>36.31484758008951</v>
+        <v>65.23222620867929</v>
       </c>
     </row>
     <row r="21">
@@ -3219,13 +3219,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>24.98104542078643</v>
+        <v>63.96119265354887</v>
       </c>
       <c r="C21" t="n">
-        <v>7.137441548796122</v>
+        <v>35.78781017519997</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.7614427696851056</v>
       </c>
     </row>
   </sheetData>
@@ -3264,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.59430151843459</v>
+        <v>19.04786895779661</v>
       </c>
       <c r="C2" t="n">
-        <v>3.223077713042279</v>
+        <v>3.457715414357266</v>
       </c>
       <c r="D2" t="n">
-        <v>55.6660765784984</v>
+        <v>59.52827204700535</v>
       </c>
     </row>
     <row r="3">
@@ -3278,13 +3278,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.92733497435251</v>
+        <v>21.83406894244906</v>
       </c>
       <c r="C3" t="n">
-        <v>2.729258617806133</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D3" t="n">
-        <v>31.88225669541517</v>
+        <v>31.64663724639593</v>
       </c>
     </row>
     <row r="4">
@@ -3292,13 +3292,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.033780332571891</v>
+        <v>0.9699667317958486</v>
       </c>
       <c r="C4" t="n">
-        <v>1.544289138780233</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
-        <v>54.76483218599983</v>
+        <v>55.50506995500192</v>
       </c>
     </row>
     <row r="5">
@@ -3306,13 +3306,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.748893571891069</v>
+        <v>2.650718801466388</v>
       </c>
       <c r="C5" t="n">
-        <v>1.742602175038089</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="D5" t="n">
-        <v>25.30454707696154</v>
+        <v>27.39076094848602</v>
       </c>
     </row>
     <row r="6">
@@ -3320,13 +3320,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.347178834404877</v>
+        <v>4.22642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>2.052834449580081</v>
+        <v>2.012582793705962</v>
       </c>
       <c r="D6" t="n">
-        <v>32.68434456978482</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -3334,13 +3334,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
         <v>2.575124228239384</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -3348,13 +3348,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>3.087596529856218</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="D8" t="n">
-        <v>50.82016991033613</v>
+        <v>49.90223580686537</v>
       </c>
     </row>
     <row r="9">
@@ -3362,13 +3362,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
         <v>3.439062207976575</v>
       </c>
       <c r="D9" t="n">
-        <v>60.23905738488002</v>
+        <v>58.68593251676156</v>
       </c>
     </row>
     <row r="10">
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>64.77080478768332</v>
+        <v>65.90963212460962</v>
       </c>
     </row>
     <row r="11">
@@ -3393,10 +3393,10 @@
         <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>70.90083745300038</v>
+        <v>70.36774844959437</v>
       </c>
     </row>
     <row r="12">
@@ -3404,7 +3404,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.292021036517808</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>4.122358610132356</v>
@@ -3418,13 +3418,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.983752257384309</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>71.80502708861172</v>
+        <v>72.84567965511333</v>
       </c>
     </row>
     <row r="14">
@@ -3432,13 +3432,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>5.838453597155781</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>70.67601722872789</v>
+        <v>71.59787832301564</v>
       </c>
     </row>
     <row r="15">
@@ -3446,13 +3446,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.091744504851459</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>70.59256867386689</v>
+        <v>72.02592032206724</v>
       </c>
     </row>
     <row r="16">
@@ -3460,13 +3460,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>63.6506306571377</v>
+        <v>71.91694632689584</v>
       </c>
     </row>
     <row r="17">
@@ -3477,10 +3477,10 @@
         <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>6.611089040398022</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>59.97202200932491</v>
       </c>
     </row>
     <row r="18">
@@ -3491,10 +3491,10 @@
         <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40935740160447</v>
+        <v>51.90009238500763</v>
       </c>
     </row>
     <row r="19">
@@ -3502,13 +3502,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>7.221736112439537</v>
+      </c>
+      <c r="C19" t="n">
         <v>7.823547455142832</v>
       </c>
-      <c r="C19" t="n">
-        <v>9.628981483252716</v>
-      </c>
       <c r="D19" t="n">
-        <v>27.68332176435156</v>
+        <v>42.12679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -3519,10 +3519,10 @@
         <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>9.41496048372691</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>8.742463306317845</v>
+        <v>28.24488145118073</v>
       </c>
     </row>
     <row r="21">
@@ -3530,13 +3530,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>12.42347521557438</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.64700801460098</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.7764672009733988</v>
       </c>
     </row>
   </sheetData>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.754424205218055</v>
+        <v>7.309111658117502</v>
       </c>
       <c r="C2" t="n">
-        <v>2.290417394007808</v>
+        <v>2.471058971589222</v>
       </c>
       <c r="D2" t="n">
-        <v>53.40412986791375</v>
+        <v>57.62760849158352</v>
       </c>
     </row>
     <row r="3">
@@ -3589,13 +3589,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>68.99231991594461</v>
+        <v>69.85625789568179</v>
       </c>
       <c r="C3" t="n">
-        <v>5.419247327442394</v>
+        <v>5.743224069843841</v>
       </c>
       <c r="D3" t="n">
-        <v>42.43604451606838</v>
+        <v>42.84346981333081</v>
       </c>
     </row>
     <row r="4">
@@ -3603,13 +3603,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.35496036724339</v>
+        <v>43.15075684476006</v>
       </c>
       <c r="C4" t="n">
-        <v>2.897137475232337</v>
+        <v>2.986476516318797</v>
       </c>
       <c r="D4" t="n">
-        <v>54.44576418211961</v>
+        <v>54.81588306662066</v>
       </c>
     </row>
     <row r="5">
@@ -3617,13 +3617,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.938951715887451</v>
+        <v>1.767145867644259</v>
       </c>
       <c r="C5" t="n">
         <v>1.988039101099791</v>
       </c>
       <c r="D5" t="n">
-        <v>27.58711048933538</v>
+        <v>30.85142160595602</v>
       </c>
     </row>
     <row r="6">
@@ -3631,13 +3631,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.306927178530758</v>
+        <v>4.065417243286043</v>
       </c>
       <c r="C6" t="n">
         <v>2.173589417202439</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>31.91956310817655</v>
       </c>
     </row>
     <row r="7">
@@ -3645,13 +3645,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
         <v>2.635010838198439</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -3659,13 +3659,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>3.171045084717197</v>
+        <v>3.087596529856218</v>
       </c>
       <c r="D8" t="n">
-        <v>50.48637569089222</v>
+        <v>49.81878725200438</v>
       </c>
     </row>
     <row r="9">
@@ -3673,13 +3673,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
         <v>3.439062207976575</v>
       </c>
       <c r="D9" t="n">
-        <v>59.46249495082079</v>
+        <v>57.79843259212245</v>
       </c>
     </row>
     <row r="10">
@@ -3690,10 +3690,10 @@
         <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>64.48609795345175</v>
+        <v>64.9131582047991</v>
       </c>
     </row>
     <row r="11">
@@ -3704,10 +3704,10 @@
         <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>69.30157044278232</v>
+        <v>69.479266777251</v>
       </c>
     </row>
     <row r="12">
@@ -3715,13 +3715,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.942919764433443</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>70.51402885752715</v>
+        <v>70.7309951001657</v>
       </c>
     </row>
     <row r="13">
@@ -3729,13 +3729,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.243915399009714</v>
+        <v>6.764241682260525</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>70.7643745221101</v>
+        <v>72.58551651348793</v>
       </c>
     </row>
     <row r="14">
@@ -3743,13 +3743,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>6.453027660014286</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>69.13958207158163</v>
+        <v>70.67601722872789</v>
       </c>
     </row>
     <row r="15">
@@ -3757,13 +3757,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.091744504851459</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>67.36752746541613</v>
+        <v>70.95090658591698</v>
       </c>
     </row>
     <row r="16">
@@ -3771,13 +3771,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>70.67699897643212</v>
       </c>
     </row>
     <row r="17">
@@ -3785,13 +3785,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>6.611089040398022</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>50.05538844872788</v>
+        <v>59.4998013635822</v>
       </c>
     </row>
     <row r="18">
@@ -3799,13 +3799,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="D18" t="n">
-        <v>37.98872741583033</v>
+        <v>51.90009238500763</v>
       </c>
     </row>
     <row r="19">
@@ -3816,10 +3816,10 @@
         <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
-        <v>9.027170140549421</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="D19" t="n">
-        <v>19.85977430920873</v>
+        <v>41.52498264652733</v>
       </c>
     </row>
     <row r="20">
@@ -3827,13 +3827,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
-        <v>6.052474596681584</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="D20" t="n">
-        <v>4.707480241863455</v>
+        <v>27.57238427377166</v>
       </c>
     </row>
     <row r="21">
@@ -3841,13 +3841,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>15.199371027991</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>12.79947033936084</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.599933792420106</v>
       </c>
     </row>
   </sheetData>
@@ -3886,13 +3886,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.203483816686347</v>
+        <v>8.982009746154068</v>
       </c>
       <c r="C2" t="n">
-        <v>2.635010838198439</v>
+        <v>2.944261365036184</v>
       </c>
       <c r="D2" t="n">
-        <v>72.56489981169874</v>
+        <v>80.27161929003621</v>
       </c>
     </row>
     <row r="3">
@@ -3900,13 +3900,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.09685853201772</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="C3" t="n">
-        <v>6.322455215349459</v>
+        <v>6.646431957750906</v>
       </c>
       <c r="D3" t="n">
-        <v>51.51721078035138</v>
+        <v>52.48914100755572</v>
       </c>
     </row>
     <row r="4">
@@ -3914,13 +3914,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>140.3899217072939</v>
+        <v>140.1346673041897</v>
       </c>
       <c r="C4" t="n">
-        <v>5.628359588446964</v>
+        <v>5.845325831085509</v>
       </c>
       <c r="D4" t="n">
-        <v>55.4667817945363</v>
+        <v>55.87518883950297</v>
       </c>
     </row>
     <row r="5">
@@ -3928,13 +3928,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.03387211469246</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="C5" t="n">
-        <v>2.748893571891069</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="D5" t="n">
-        <v>29.69786805346602</v>
+        <v>33.89483948912113</v>
       </c>
     </row>
     <row r="6">
@@ -3942,13 +3942,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.340887437551896</v>
+        <v>2.938370878810704</v>
       </c>
       <c r="C6" t="n">
         <v>2.374847696573035</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73088762251191</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -3956,13 +3956,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
         <v>2.694897448157494</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -3970,13 +3970,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>3.254493639578176</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>50.15258147144831</v>
+        <v>49.73533869714341</v>
       </c>
     </row>
     <row r="9">
@@ -3984,13 +3984,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="D9" t="n">
-        <v>58.79687000734145</v>
+        <v>57.02187015806322</v>
       </c>
     </row>
     <row r="10">
@@ -3998,13 +3998,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>64.20139111922018</v>
+        <v>64.05903770210438</v>
       </c>
     </row>
     <row r="11">
@@ -4012,13 +4012,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.818638716621595</v>
+        <v>7.996335051090269</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>67.87999976703294</v>
+        <v>68.59078510490764</v>
       </c>
     </row>
     <row r="12">
@@ -4026,13 +4026,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.593818492349078</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
         <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>69.42919764433442</v>
+        <v>69.86313012961152</v>
       </c>
     </row>
     <row r="13">
@@ -4040,13 +4040,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.764241682260525</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>69.72372195560848</v>
+        <v>72.32535337186253</v>
       </c>
     </row>
     <row r="14">
@@ -4054,13 +4054,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>6.760314691443536</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>67.29585988300612</v>
+        <v>69.75415613444012</v>
       </c>
     </row>
     <row r="15">
@@ -4068,13 +4068,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>64.50082416901544</v>
+        <v>69.87589284976671</v>
       </c>
     </row>
     <row r="16">
@@ -4082,13 +4082,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="D16" t="n">
-        <v>55.79763077086746</v>
+        <v>69.43705162596841</v>
       </c>
     </row>
     <row r="17">
@@ -4096,13 +4096,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>6.611089040398022</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="D17" t="n">
-        <v>45.33318199130072</v>
+        <v>59.4998013635822</v>
       </c>
     </row>
     <row r="18">
@@ -4110,13 +4110,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>7.490734983403163</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>50.82998738737861</v>
       </c>
     </row>
     <row r="19">
@@ -4127,10 +4127,10 @@
         <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>7.823547455142832</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="D19" t="n">
-        <v>13.23984953947248</v>
+        <v>40.92317130382404</v>
       </c>
     </row>
     <row r="20">
@@ -4138,13 +4138,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.362485887045325</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>3.362485887045325</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="D20" t="n">
-        <v>2.017491532227195</v>
+        <v>27.57238427377166</v>
       </c>
     </row>
     <row r="21">
@@ -4152,13 +4152,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>18.11602916342552</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13.99874980810154</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.470367613194389</v>
       </c>
     </row>
   </sheetData>
@@ -4197,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16.82911914619882</v>
+        <v>17.47314564018473</v>
       </c>
       <c r="C2" t="n">
-        <v>1.867284133477433</v>
+        <v>2.138246499849553</v>
       </c>
       <c r="D2" t="n">
-        <v>68.66245268731767</v>
+        <v>76.78346969684729</v>
       </c>
     </row>
     <row r="3">
@@ -4211,13 +4211,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.5203927031756</v>
+        <v>34.69987260660351</v>
       </c>
       <c r="C3" t="n">
-        <v>7.289476704032568</v>
+        <v>7.726354432422397</v>
       </c>
       <c r="D3" t="n">
-        <v>64.39774066006953</v>
+        <v>66.63121668723102</v>
       </c>
     </row>
     <row r="4">
@@ -4225,13 +4225,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81.27300194836796</v>
+        <v>83.20017269180444</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10432729855742</v>
+        <v>8.346818981506383</v>
       </c>
       <c r="D4" t="n">
-        <v>57.54710517983528</v>
+        <v>58.27458022868218</v>
       </c>
     </row>
     <row r="5">
@@ -4239,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>199.073890728647</v>
+        <v>199.9820073550753</v>
       </c>
       <c r="C5" t="n">
-        <v>4.466952054322988</v>
+        <v>4.761476365597031</v>
       </c>
       <c r="D5" t="n">
-        <v>32.0295188510522</v>
+        <v>36.76645152404306</v>
       </c>
     </row>
     <row r="6">
@@ -4253,13 +4253,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.88316599432396</v>
+        <v>72.89574878802993</v>
       </c>
       <c r="C6" t="n">
-        <v>2.777364255314227</v>
+        <v>2.857867567062466</v>
       </c>
       <c r="D6" t="n">
-        <v>33.93214590188251</v>
+        <v>32.92585450502953</v>
       </c>
     </row>
     <row r="7">
@@ -4267,13 +4267,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>2.87455727803466</v>
+        <v>2.814670668075606</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -4281,13 +4281,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>3.254493639578176</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>49.81878725200438</v>
+        <v>49.06775025825559</v>
       </c>
     </row>
     <row r="9">
@@ -4295,13 +4295,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>3.660937189136355</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>58.13124506386212</v>
+        <v>56.24530772400399</v>
       </c>
     </row>
     <row r="10">
@@ -4309,13 +4309,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>63.77433086787281</v>
+        <v>63.20491719940966</v>
       </c>
     </row>
     <row r="11">
@@ -4326,10 +4326,10 @@
         <v>8.529424054496287</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>66.99151809468958</v>
+        <v>67.70230343256426</v>
       </c>
     </row>
     <row r="12">
@@ -4337,13 +4337,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.244717220264713</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C12" t="n">
         <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>69.64616388697297</v>
       </c>
     </row>
     <row r="13">
@@ -4351,13 +4351,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.284567965511334</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>68.68306938910686</v>
+        <v>71.28470080536091</v>
       </c>
     </row>
     <row r="14">
@@ -4365,13 +4365,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.453027660014286</v>
+        <v>7.37488875430204</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>65.14485066300135</v>
+        <v>68.83229504015237</v>
       </c>
     </row>
     <row r="15">
@@ -4379,13 +4379,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>68.80087911361647</v>
       </c>
     </row>
     <row r="16">
@@ -4393,13 +4393,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="D16" t="n">
-        <v>51.66447293598839</v>
+        <v>69.02373584248051</v>
       </c>
     </row>
     <row r="17">
@@ -4407,13 +4407,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>6.611089040398022</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="D17" t="n">
-        <v>40.13875488813085</v>
+        <v>58.55536007209676</v>
       </c>
     </row>
     <row r="18">
@@ -4421,13 +4421,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>6.955682484588652</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>24.61241494546753</v>
+        <v>50.2949348885641</v>
       </c>
     </row>
     <row r="19">
@@ -4435,13 +4435,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>6.018113427032947</v>
       </c>
       <c r="D19" t="n">
-        <v>8.425358797846126</v>
+        <v>40.32135996112075</v>
       </c>
     </row>
     <row r="20">
@@ -4449,13 +4449,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017491532227195</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>2.017491532227195</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="D20" t="n">
-        <v>0.672497177409065</v>
+        <v>26.8998870963626</v>
       </c>
     </row>
     <row r="21">
@@ -4463,13 +4463,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>20.31521673059498</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>14.38994518417144</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.385869455099163</v>
       </c>
     </row>
   </sheetData>
@@ -4508,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.45413258090555</v>
+        <v>21.72214970416493</v>
       </c>
       <c r="C2" t="n">
-        <v>1.474585051778709</v>
+        <v>1.731802950291373</v>
       </c>
       <c r="D2" t="n">
-        <v>74.64129620618074</v>
+        <v>85.07432905921159</v>
       </c>
     </row>
     <row r="3">
@@ -4522,13 +4522,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>61.53103736366884</v>
+        <v>62.22807823368407</v>
       </c>
       <c r="C3" t="n">
-        <v>7.181484456565419</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="D3" t="n">
-        <v>75.2067828838269</v>
+        <v>78.55454255530854</v>
       </c>
     </row>
     <row r="4">
@@ -4536,13 +4536,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>74.30455674362409</v>
+        <v>77.85259294677206</v>
       </c>
       <c r="C4" t="n">
-        <v>10.42714236680537</v>
+        <v>10.70792221021996</v>
       </c>
       <c r="D4" t="n">
-        <v>61.06961594267284</v>
+        <v>62.56285420083224</v>
       </c>
     </row>
     <row r="5">
@@ -4550,13 +4550,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>151.6800203061322</v>
+        <v>150.6737289092792</v>
       </c>
       <c r="C5" t="n">
-        <v>6.700428081484483</v>
+        <v>7.215845626214058</v>
       </c>
       <c r="D5" t="n">
-        <v>34.36116964863837</v>
+        <v>39.98167525545136</v>
       </c>
     </row>
     <row r="6">
@@ -4564,13 +4564,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>243.5225180384214</v>
+        <v>247.789193561078</v>
       </c>
       <c r="C6" t="n">
-        <v>3.622649028670731</v>
+        <v>3.904410619789565</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -4578,13 +4578,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>68.92948806287281</v>
+        <v>75.33735532849173</v>
       </c>
       <c r="C7" t="n">
-        <v>3.114103717870883</v>
+        <v>3.054217107911827</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -4592,13 +4592,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>3.337942194439155</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="D8" t="n">
-        <v>49.48499303256047</v>
+        <v>48.40016181936775</v>
       </c>
     </row>
     <row r="9">
@@ -4606,13 +4606,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>3.771874679716245</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>57.46562012038278</v>
+        <v>55.46874528994476</v>
       </c>
     </row>
     <row r="10">
@@ -4620,13 +4620,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>63.34727061652544</v>
+        <v>62.35079669671494</v>
       </c>
     </row>
     <row r="11">
@@ -4634,13 +4634,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.417905726839649</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>66.10303642234622</v>
+        <v>67.5246070980956</v>
       </c>
     </row>
     <row r="12">
@@ -4654,7 +4654,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>66.60863649003335</v>
+        <v>68.56133267378024</v>
       </c>
     </row>
     <row r="13">
@@ -4662,13 +4662,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.804894248762142</v>
+        <v>8.585383673638358</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>66.60176425610362</v>
+        <v>70.24404823885929</v>
       </c>
     </row>
     <row r="14">
@@ -4676,13 +4676,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.760314691443536</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>62.99384144299659</v>
+        <v>67.91043394586463</v>
       </c>
     </row>
     <row r="15">
@@ -4690,13 +4690,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>58.05074175211389</v>
+        <v>67.72586537746622</v>
       </c>
     </row>
     <row r="16">
@@ -4704,13 +4704,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="D16" t="n">
-        <v>47.53131510110933</v>
+        <v>68.61042005899259</v>
       </c>
     </row>
     <row r="17">
@@ -4718,13 +4718,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>6.611089040398022</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>34.47210713921825</v>
+        <v>57.61091878061134</v>
       </c>
     </row>
     <row r="18">
@@ -4735,10 +4735,10 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>18.1917849596934</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="19">
@@ -4746,13 +4746,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>4.212679398923063</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="D19" t="n">
-        <v>4.814490741626358</v>
+        <v>39.71954861841746</v>
       </c>
     </row>
     <row r="20">
@@ -4760,13 +4760,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>0.672497177409065</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26.8998870963626</v>
       </c>
     </row>
     <row r="21">
@@ -4774,13 +4774,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>21.72143097358756</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>14.77057306203954</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.47542895577401</v>
       </c>
     </row>
   </sheetData>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.77564710627976</v>
+        <v>32.32207966691774</v>
       </c>
       <c r="C2" t="n">
-        <v>1.079922474671491</v>
+        <v>1.299833960422777</v>
       </c>
       <c r="D2" t="n">
-        <v>90.86664051426779</v>
+        <v>105.2541531200048</v>
       </c>
     </row>
     <row r="3">
@@ -4833,13 +4833,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>79.32521450314228</v>
+        <v>78.75580083467912</v>
       </c>
       <c r="C3" t="n">
-        <v>6.720063035569417</v>
+        <v>7.274750488468865</v>
       </c>
       <c r="D3" t="n">
-        <v>84.23395302437633</v>
+        <v>91.30253649495336</v>
       </c>
     </row>
     <row r="4">
@@ -4847,13 +4847,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>122.7646051729509</v>
+        <v>121.9988419636384</v>
       </c>
       <c r="C4" t="n">
-        <v>12.02248238620644</v>
+        <v>12.43088943117311</v>
       </c>
       <c r="D4" t="n">
-        <v>64.37516046287185</v>
+        <v>68.81658707688442</v>
       </c>
     </row>
     <row r="5">
@@ -4861,13 +4861,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>132.1186972990145</v>
+        <v>134.7448724078747</v>
       </c>
       <c r="C5" t="n">
-        <v>9.22842841992002</v>
+        <v>9.743845964649594</v>
       </c>
       <c r="D5" t="n">
-        <v>35.68652904937156</v>
+        <v>42.21515128261285</v>
       </c>
     </row>
     <row r="6">
@@ -4875,13 +4875,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>239.6181074186318</v>
+        <v>233.0570875111503</v>
       </c>
       <c r="C6" t="n">
-        <v>4.950953672516666</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="D6" t="n">
-        <v>34.81768233111314</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4889,13 +4889,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243.079749823806</v>
+        <v>257.9915157036108</v>
       </c>
       <c r="C7" t="n">
-        <v>3.473423377625215</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -4903,13 +4903,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56.16087742143878</v>
+        <v>66.92574099850506</v>
       </c>
       <c r="C8" t="n">
-        <v>3.421390749300134</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="D8" t="n">
-        <v>49.15119881311656</v>
+        <v>47.73257338047992</v>
       </c>
     </row>
     <row r="9">
@@ -4917,13 +4917,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.096874227550941</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>3.882812170296134</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>57.35468262980289</v>
+        <v>55.24687030878498</v>
       </c>
     </row>
     <row r="10">
@@ -4931,13 +4931,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.53415286656828</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>62.20844327959914</v>
+        <v>61.35432277690443</v>
       </c>
     </row>
     <row r="11">
@@ -4945,13 +4945,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10.30638739918301</v>
+        <v>10.12869106471434</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>65.21455475000286</v>
+        <v>66.45842909128358</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4965,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>65.30683903420207</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -4973,13 +4973,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.325220532012953</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>64.52045912310038</v>
+        <v>69.20339567235767</v>
       </c>
     </row>
     <row r="14">
@@ -4987,13 +4987,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.067601722872788</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>60.53554519156258</v>
+        <v>66.98857285157686</v>
       </c>
     </row>
     <row r="15">
@@ -5001,13 +5001,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>54.82570054366312</v>
+        <v>67.36752746541613</v>
       </c>
     </row>
     <row r="16">
@@ -5018,10 +5018,10 @@
         <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="D16" t="n">
-        <v>42.98484148274235</v>
+        <v>67.37047270852887</v>
       </c>
     </row>
     <row r="17">
@@ -5029,13 +5029,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>6.138868394655306</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>28.80545939030567</v>
+        <v>56.6664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -5043,13 +5043,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="D18" t="n">
-        <v>12.84125997154828</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -5057,13 +5057,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3.009056713516474</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>3.009056713516474</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="D19" t="n">
-        <v>2.407245370813179</v>
+        <v>39.11773727571416</v>
       </c>
     </row>
     <row r="20">
@@ -5071,13 +5071,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26.8998870963626</v>
       </c>
     </row>
     <row r="21">
@@ -5085,13 +5085,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22.25473057953502</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15.13321679408382</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.560756892725604</v>
       </c>
     </row>
   </sheetData>
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.34674653271092</v>
+        <v>46.46611884200153</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7755806863549802</v>
+        <v>0.9552405162321465</v>
       </c>
       <c r="D2" t="n">
-        <v>93.20320005037519</v>
+        <v>109.6896892477919</v>
       </c>
     </row>
     <row r="3">
@@ -5144,13 +5144,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>115.2620892170968</v>
+        <v>110.6282400530518</v>
       </c>
       <c r="C3" t="n">
-        <v>6.042657119639118</v>
+        <v>6.607162049581034</v>
       </c>
       <c r="D3" t="n">
-        <v>95.79894098040376</v>
+        <v>104.3156023147449</v>
       </c>
     </row>
     <row r="4">
@@ -5158,13 +5158,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>160.6954094742306</v>
+        <v>155.3733551695087</v>
       </c>
       <c r="C4" t="n">
-        <v>12.8648219164502</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D4" t="n">
-        <v>68.34436643114171</v>
+        <v>74.15140410176159</v>
       </c>
     </row>
     <row r="5">
@@ -5172,13 +5172,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>181.5006068226291</v>
+        <v>178.2362957060084</v>
       </c>
       <c r="C5" t="n">
-        <v>11.46190444708151</v>
+        <v>12.2963899956913</v>
       </c>
       <c r="D5" t="n">
-        <v>37.13460691313561</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="6">
@@ -5186,13 +5186,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>216.4734052910133</v>
+        <v>212.2872330801048</v>
       </c>
       <c r="C6" t="n">
-        <v>6.722026530977913</v>
+        <v>7.406304680837938</v>
       </c>
       <c r="D6" t="n">
-        <v>35.783722072092</v>
+        <v>35.26045054572845</v>
       </c>
     </row>
     <row r="7">
@@ -5200,13 +5200,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299.7324828450724</v>
+        <v>295.6003067578976</v>
       </c>
       <c r="C7" t="n">
-        <v>4.012402867256713</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -5214,13 +5214,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>200.6103258857932</v>
+        <v>230.6518056357456</v>
       </c>
       <c r="C8" t="n">
         <v>3.588287859022091</v>
       </c>
       <c r="D8" t="n">
-        <v>48.73395603881166</v>
+        <v>47.06498494159209</v>
       </c>
     </row>
     <row r="9">
@@ -5228,13 +5228,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39.71562162760046</v>
+        <v>52.25155806312797</v>
       </c>
       <c r="C9" t="n">
-        <v>3.882812170296134</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="D9" t="n">
-        <v>56.57812019574367</v>
+        <v>54.35937038414588</v>
       </c>
     </row>
     <row r="10">
@@ -5242,13 +5242,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.67650628368406</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>61.06961594267285</v>
+        <v>60.50020227420969</v>
       </c>
     </row>
     <row r="11">
@@ -5256,13 +5256,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.0171727370577</v>
+        <v>10.48408373365169</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3260730776595</v>
+        <v>65.39225108447152</v>
       </c>
     </row>
     <row r="12">
@@ -5276,7 +5276,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="D12" t="n">
-        <v>64.00504157837081</v>
+        <v>66.82560273267188</v>
       </c>
     </row>
     <row r="13">
@@ -5284,13 +5284,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="C13" t="n">
         <v>3.902447124381071</v>
       </c>
       <c r="D13" t="n">
-        <v>62.43915399009714</v>
+        <v>68.94323253073227</v>
       </c>
     </row>
     <row r="14">
@@ -5298,13 +5298,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.37488875430204</v>
+        <v>8.911323911448299</v>
       </c>
       <c r="C14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>58.38453597155782</v>
+        <v>66.06671175728911</v>
       </c>
     </row>
     <row r="15">
@@ -5312,13 +5312,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>50.52564559906209</v>
+        <v>66.29251372926586</v>
       </c>
     </row>
     <row r="16">
@@ -5329,10 +5329,10 @@
         <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="D16" t="n">
-        <v>38.43836786437537</v>
+        <v>66.13052535806514</v>
       </c>
     </row>
     <row r="17">
@@ -5343,10 +5343,10 @@
         <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -5354,13 +5354,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.280419990516093</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
         <v>4.280419990516093</v>
       </c>
       <c r="D18" t="n">
-        <v>9.095892479846698</v>
+        <v>48.15472489330605</v>
       </c>
     </row>
     <row r="19">
@@ -5368,13 +5368,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.805434028109884</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>1.805434028109884</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="D19" t="n">
-        <v>1.203622685406589</v>
+        <v>39.11773727571416</v>
       </c>
     </row>
     <row r="20">
@@ -5382,13 +5382,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26.22738991895353</v>
       </c>
     </row>
     <row r="21">
@@ -5396,13 +5396,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22.75137688227239</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15.47093627994522</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.640220301163582</v>
       </c>
     </row>
   </sheetData>
